--- a/Task4/Роли кластера.xlsx
+++ b/Task4/Роли кластера.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои_документы\Курсы\Учеба\sprint_7\architecture-propdevelopment\Task4\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6846805C-FB99-4A54-AEF6-5FF1B08ABAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="24240" windowHeight="13740"/>
+    <workbookView xWindow="1200" yWindow="2655" windowWidth="18000" windowHeight="9480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">Роль </t>
   </si>
@@ -25,37 +31,46 @@
     <t>Группы пользователей</t>
   </si>
   <si>
-    <t>cluster_admin</t>
-  </si>
-  <si>
-    <t>Администраторы кластера, полный набор прав</t>
-  </si>
-  <si>
-    <t>Пользователи кластера с правами просмотра</t>
-  </si>
-  <si>
-    <t>cluster_worker</t>
-  </si>
-  <si>
-    <t>Пользователи кластера с правами просмотра и редактирования</t>
-  </si>
-  <si>
-    <t>get, list, watch</t>
-  </si>
-  <si>
-    <t>cluster_viewer</t>
-  </si>
-  <si>
-    <t>get, list, watch, update, patch</t>
-  </si>
-  <si>
-    <t>delete, сreate, get, list, watch, сreate, update, patch для всех resources</t>
+    <t>cluster-admin</t>
+  </si>
+  <si>
+    <t>cluster-viewer</t>
+  </si>
+  <si>
+    <t>cluster-worker</t>
+  </si>
+  <si>
+    <t>Пользователи кластера с правами просмотра pods</t>
+  </si>
+  <si>
+    <t>Пользователи кластера с правами просмотра и редактирования  pods</t>
+  </si>
+  <si>
+    <t>Администраторы кластера, полный набор прарав для работы с  pods и secrets</t>
+  </si>
+  <si>
+    <t>get, list, watch, update, patch для resources pods</t>
+  </si>
+  <si>
+    <t>get, list, watch для resources pods</t>
+  </si>
+  <si>
+    <t>delete, сreate, get, list, watch, сreate, update, patch для  resources pods, secrets</t>
+  </si>
+  <si>
+    <t>cluster-view-secrets</t>
+  </si>
+  <si>
+    <t>get, list для resources secrets</t>
+  </si>
+  <si>
+    <t>Пользователи кластера с правами просмотра secrets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1">
     <font>
       <sz val="10"/>
@@ -398,18 +413,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
     <col min="3" max="3" width="26.140625" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.5">
+    <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -420,7 +435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="40.5" customHeight="1">
+    <row r="2" spans="1:7" ht="52.5" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
@@ -428,26 +443,26 @@
         <v>11</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="33" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>7</v>
@@ -455,10 +470,16 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" s="5" customFormat="1">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="3"/>
+    <row r="5" spans="1:7" s="5" customFormat="1" ht="36.75" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:7" s="5" customFormat="1">
       <c r="A6" s="3"/>
